--- a/xls/square_un_16_tri3_18.xlsx
+++ b/xls/square_un_16_tri3_18.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>435</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>340</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>340</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>1842</v>
+      </c>
+      <c r="I16">
+        <v>-0.00017951565938940074</v>
+      </c>
+      <c r="J16">
+        <v>-0.8269222693517562</v>
+      </c>
+      <c r="K16">
+        <v>1.9327176393510677</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>435</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>340</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>380</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>2070</v>
+      </c>
+      <c r="I17">
+        <v>-0.0001815552540770699</v>
+      </c>
+      <c r="J17">
+        <v>-0.8250400440914458</v>
+      </c>
+      <c r="K17">
+        <v>2.0832083262034455</v>
+      </c>
+    </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>11</v>
       </c>
       <c r="B18">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>1944</v>
+        <v>2388</v>
       </c>
       <c r="I18">
-        <v>-2.3983026052375775</v>
+        <v>-9.709463248032465e-5</v>
       </c>
       <c r="J18">
-        <v>-2.2425119173010613</v>
+        <v>-0.32610274411915796</v>
       </c>
       <c r="K18">
-        <v>-0.5915685973123109</v>
+        <v>3.065731040831324</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B19">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-2.6034454190551006</v>
+        <v>-1.3579549247087485e-5</v>
       </c>
       <c r="J19">
-        <v>-2.2270650599406143</v>
+        <v>-0.03600398513182669</v>
       </c>
       <c r="K19">
-        <v>-0.04314349465063988</v>
+        <v>3.3964446008667175</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>-2.207197370223644</v>
+        <v>-1.2485359076648889e-8</v>
       </c>
       <c r="J20">
-        <v>-1.8007019486154898</v>
+        <v>-2.4346410887161355e-5</v>
       </c>
       <c r="K20">
-        <v>0.7843929079219154</v>
+        <v>2.1399509950825655</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.7120091553397088</v>
+        <v>-7.682933349891688e-9</v>
       </c>
       <c r="J21">
-        <v>-1.442385816008792</v>
+        <v>-1.4156041759179371e-5</v>
       </c>
       <c r="K21">
-        <v>1.6843656346657105</v>
+        <v>2.0124316865523055</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-0.16705021680175905</v>
+        <v>-4.2193230464251926e-9</v>
       </c>
       <c r="J22">
-        <v>-0.14561949574806254</v>
+        <v>-7.254664356710192e-6</v>
       </c>
       <c r="K22">
-        <v>3.4169289025049143</v>
+        <v>1.8639286924815357</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-0.0010483531863086264</v>
+        <v>-2.221020318691927e-9</v>
       </c>
       <c r="J23">
-        <v>-0.0013372929829357904</v>
+        <v>-3.868164936359552e-6</v>
       </c>
       <c r="K23">
-        <v>3.0364531283499296</v>
+        <v>1.7315724054712969</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-0.00016551019494743575</v>
+        <v>-1.821387730102012e-9</v>
       </c>
       <c r="J24">
-        <v>-0.0002160976196344011</v>
+        <v>-3.4021324830831102e-6</v>
       </c>
       <c r="K24">
-        <v>2.6667150376386206</v>
+        <v>1.710389655055536</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-9.136996215152321e-5</v>
+        <v>-1.2059677286855082e-9</v>
       </c>
       <c r="J25">
-        <v>-0.00010596626013044341</v>
+        <v>-2.190494752183118e-6</v>
       </c>
       <c r="K25">
-        <v>2.492157866335209</v>
+        <v>1.6114605144940342</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-5.3500232069182806e-5</v>
+        <v>-9.701250525821093e-10</v>
       </c>
       <c r="J26">
-        <v>-5.842247084147352e-5</v>
+        <v>-1.7859471824321646e-6</v>
       </c>
       <c r="K26">
-        <v>2.3524658724222367</v>
+        <v>1.5702506540156531</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-4.0816164685586494e-5</v>
+        <v>-7.773140916017857e-10</v>
       </c>
       <c r="J27">
-        <v>-4.5369845646230706e-5</v>
+        <v>-1.4655866755208976e-6</v>
       </c>
       <c r="K27">
-        <v>2.302753250732842</v>
+        <v>1.5281645034138542</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-3.114262766075616e-5</v>
+        <v>-8.470515539964306e-10</v>
       </c>
       <c r="J28">
-        <v>-3.461681804490181e-5</v>
+        <v>-1.588575809858773e-6</v>
       </c>
       <c r="K28">
-        <v>2.2431956324389337</v>
+        <v>1.545996886613057</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-2.471541855637145e-5</v>
+        <v>-8.55754657615509e-10</v>
       </c>
       <c r="J29">
-        <v>-2.6913513638510794e-5</v>
+        <v>-1.5677512584386045e-6</v>
       </c>
       <c r="K29">
-        <v>2.185800975262199</v>
+        <v>1.541376348370832</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -881,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-1.9711398029773872e-5</v>
+        <v>-6.729499924416684e-10</v>
       </c>
       <c r="J30">
-        <v>-2.1367289732195488e-5</v>
+        <v>-1.210363776460235e-6</v>
       </c>
       <c r="K30">
-        <v>2.1334934392687153</v>
+        <v>1.4818452339568622</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -916,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-1.6787915558340534e-5</v>
+        <v>-6.496841940008161e-10</v>
       </c>
       <c r="J31">
-        <v>-1.8361322475546828e-5</v>
+        <v>-1.178039657322299e-6</v>
       </c>
       <c r="K31">
-        <v>2.1024561948187213</v>
+        <v>1.4777998119370146</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -951,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -963,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-1.3167192824828266e-5</v>
+        <v>-5.426319838386116e-10</v>
       </c>
       <c r="J32">
-        <v>-1.4115754754954127e-5</v>
+        <v>-1.0014977357828397e-6</v>
       </c>
       <c r="K32">
-        <v>2.0418151629915653</v>
+        <v>1.4436584791979874</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_18.xlsx
+++ b/xls/square_un_16_tri3_18.xlsx
@@ -482,13 +482,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-0.00017951565938940074</v>
+        <v>-1.7419888551844995</v>
       </c>
       <c r="J16">
-        <v>-0.8269222693517562</v>
+        <v>-1.9768402590646135</v>
       </c>
       <c r="K16">
-        <v>1.9327176393510677</v>
+        <v>-0.8942698591515683</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2070</v>
       </c>
       <c r="I17">
-        <v>-0.0001815552540770699</v>
+        <v>-2.2698640860875785</v>
       </c>
       <c r="J17">
-        <v>-0.8250400440914458</v>
+        <v>-1.8708960585167864</v>
       </c>
       <c r="K17">
-        <v>2.0832083262034455</v>
+        <v>-0.021911086248728926</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-9.709463248032465e-5</v>
+        <v>-2.006452108944688</v>
       </c>
       <c r="J18">
-        <v>-0.32610274411915796</v>
+        <v>-1.6458548960714279</v>
       </c>
       <c r="K18">
-        <v>3.065731040831324</v>
+        <v>0.5024661844514586</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-1.3579549247087485e-5</v>
+        <v>-0.8359189661190873</v>
       </c>
       <c r="J19">
-        <v>-0.03600398513182669</v>
+        <v>-0.7321734241867027</v>
       </c>
       <c r="K19">
-        <v>3.3964446008667175</v>
+        <v>1.6975380818175652</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -622,13 +622,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-1.2485359076648889e-8</v>
+        <v>0.0005244984640021995</v>
       </c>
       <c r="J20">
-        <v>-2.4346410887161355e-5</v>
+        <v>5.5784225280724935e-5</v>
       </c>
       <c r="K20">
-        <v>2.1399509950825655</v>
+        <v>2.6155149016169603</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -657,13 +657,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-7.682933349891688e-9</v>
+        <v>1.334064558492133e-5</v>
       </c>
       <c r="J21">
-        <v>-1.4156041759179371e-5</v>
+        <v>-8.178078406494895e-6</v>
       </c>
       <c r="K21">
-        <v>2.0124316865523055</v>
+        <v>2.233022790697836</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -692,13 +692,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-4.2193230464251926e-9</v>
+        <v>-9.69265582891044e-6</v>
       </c>
       <c r="J22">
-        <v>-7.254664356710192e-6</v>
+        <v>-9.579412308503748e-6</v>
       </c>
       <c r="K22">
-        <v>1.8639286924815357</v>
+        <v>1.9425704106080501</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -727,13 +727,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-2.221020318691927e-9</v>
+        <v>-1.717737968046056e-6</v>
       </c>
       <c r="J23">
-        <v>-3.868164936359552e-6</v>
+        <v>-2.9666887133442693e-6</v>
       </c>
       <c r="K23">
-        <v>1.7315724054712969</v>
+        <v>1.7757404199957394</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -762,13 +762,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-1.821387730102012e-9</v>
+        <v>-3.1957583351473703e-6</v>
       </c>
       <c r="J24">
-        <v>-3.4021324830831102e-6</v>
+        <v>-3.47704755762568e-6</v>
       </c>
       <c r="K24">
-        <v>1.710389655055536</v>
+        <v>1.7417669878056043</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -797,13 +797,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-1.2059677286855082e-9</v>
+        <v>-1.8802713350452605e-6</v>
       </c>
       <c r="J25">
-        <v>-2.190494752183118e-6</v>
+        <v>-2.1119434306691686e-6</v>
       </c>
       <c r="K25">
-        <v>1.6114605144940342</v>
+        <v>1.6444685503960614</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -832,13 +832,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-9.701250525821093e-10</v>
+        <v>-1.5329966881445803e-6</v>
       </c>
       <c r="J26">
-        <v>-1.7859471824321646e-6</v>
+        <v>-1.719251064918505e-6</v>
       </c>
       <c r="K26">
-        <v>1.5702506540156531</v>
+        <v>1.5986823484750141</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -867,13 +867,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-7.773140916017857e-10</v>
+        <v>-1.1132269787902566e-6</v>
       </c>
       <c r="J27">
-        <v>-1.4655866755208976e-6</v>
+        <v>-1.3335212884830993e-6</v>
       </c>
       <c r="K27">
-        <v>1.5281645034138542</v>
+        <v>1.5564195729056567</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -902,13 +902,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-8.470515539964306e-10</v>
+        <v>-1.7921698118560746e-6</v>
       </c>
       <c r="J28">
-        <v>-1.588575809858773e-6</v>
+        <v>-1.7295693775719119e-6</v>
       </c>
       <c r="K28">
-        <v>1.545996886613057</v>
+        <v>1.5635903144381949</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -937,13 +937,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-8.55754657615509e-10</v>
+        <v>-1.8959536698251536e-6</v>
       </c>
       <c r="J29">
-        <v>-1.5677512584386045e-6</v>
+        <v>-1.7662885646375534e-6</v>
       </c>
       <c r="K29">
-        <v>1.541376348370832</v>
+        <v>1.561004003635263</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -972,13 +972,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-6.729499924416684e-10</v>
+        <v>-1.1618741278388226e-6</v>
       </c>
       <c r="J30">
-        <v>-1.210363776460235e-6</v>
+        <v>-1.209399692886421e-6</v>
       </c>
       <c r="K30">
-        <v>1.4818452339568622</v>
+        <v>1.5047573638567655</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-6.496841940008161e-10</v>
+        <v>-1.1471931013069875e-6</v>
       </c>
       <c r="J31">
-        <v>-1.178039657322299e-6</v>
+        <v>-1.1695113168561495e-6</v>
       </c>
       <c r="K31">
-        <v>1.4777998119370146</v>
+        <v>1.4954616796275495</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-5.426319838386116e-10</v>
+        <v>-1.0031258499090845e-6</v>
       </c>
       <c r="J32">
-        <v>-1.0014977357828397e-6</v>
+        <v>-1.0114159363857157e-6</v>
       </c>
       <c r="K32">
-        <v>1.4436584791979874</v>
+        <v>1.4585473309070904</v>
       </c>
     </row>
   </sheetData>
